--- a/education_forms/032_high_school_counselor_information_form--education_forms.xlsx
+++ b/education_forms/032_high_school_counselor_information_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_11}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 11}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_9}</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 9}</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_10}</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 10}</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_11}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 11}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_12}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 12}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_13}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 13}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_14}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 14}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_15}</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 15}</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_16}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 16}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1432,301 +1432,233 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_17}</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 17}</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>user_type_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_18}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 18}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>user_type_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_19}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 19}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>user_type_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_20}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 20}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_21}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 21}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>user_type_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'student'}</t>
+          <t>teacher_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Student'}</t>
+          <t>Teacher 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>user_type_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'parent'}</t>
+          <t>teacher_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Parent'}</t>
+          <t>Teacher 2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>user_type_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'teacher'}</t>
+          <t>teacher_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Teacher'}</t>
+          <t>Teacher 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'teacher_1'}</t>
+          <t>teacher_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Teacher 1'}</t>
+          <t>Teacher 2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'teacher_2'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Teacher 2'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>assigned_to_2_choices</t>
+          <t>submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'teacher'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Teacher'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>assigned_to_2_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'teacher_1'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Teacher 1'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>assigned_to_2_choices</t>
+          <t>submitted_by_3_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'teacher_2'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Teacher 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'john_smith'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'John Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>submitted_by_3_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'john_smith'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'John Smith'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>submitted_by_3_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
